--- a/data/工作流规则_Java类分词.xlsx
+++ b/data/工作流规则_Java类分词.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github_code_lib\keyword_classifier_by_workflow\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7E7FDD-7912-46FD-9739-6581640133C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE0CDC3-74BB-4983-9CA5-5C3BB0F4D5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="327">
   <si>
     <t>分类规则</t>
   </si>
@@ -1036,6 +1036,10 @@
   </si>
   <si>
     <t>课工场</t>
+  </si>
+  <si>
+    <t>测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4137,7 +4141,7 @@
         <v>304</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4154,7 +4158,7 @@
         <v>304</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4171,7 +4175,7 @@
         <v>304</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4188,7 +4192,7 @@
         <v>304</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4205,7 +4209,7 @@
         <v>304</v>
       </c>
       <c r="E6" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4222,7 +4226,7 @@
         <v>304</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4239,7 +4243,7 @@
         <v>304</v>
       </c>
       <c r="E8" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4256,7 +4260,7 @@
         <v>304</v>
       </c>
       <c r="E9" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
